--- a/founded bug/data/VECT.xlsx
+++ b/founded bug/data/VECT.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\learning\matafeiyanll.github.io\founded bug\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="23040" windowHeight="10455"/>
   </bookViews>
   <sheets>
     <sheet name="Bugs" sheetId="1" r:id="rId1"/>
@@ -145,7 +145,7 @@
     <t>https://github.com/alibaba/AliSQL/issues/186</t>
   </si>
   <si>
-    <t>CRATEDB</t>
+    <t>CrateDB</t>
   </si>
   <si>
     <t>#19760</t>
@@ -181,7 +181,7 @@
     <t>https://github.com/crate/crate/issues/20136</t>
   </si>
   <si>
-    <t>DUCKDB</t>
+    <t>DuckDB</t>
   </si>
   <si>
     <t>#25148</t>
@@ -190,7 +190,7 @@
     <t>https://github.com/duckdb/duckdb/issues/25148</t>
   </si>
   <si>
-    <t>MARIADB</t>
+    <t>MariaDB</t>
   </si>
   <si>
     <t>MDEV-39580</t>
@@ -235,7 +235,7 @@
     <t>https://jira.mariadb.org/browse/MDEV-40893</t>
   </si>
   <si>
-    <t>MONETDB</t>
+    <t>MonetDB</t>
   </si>
   <si>
     <t>#7999</t>
@@ -286,7 +286,7 @@
     <t>https://github.com/MonetDB/MonetDB/issues/8019</t>
   </si>
   <si>
-    <t>MYSQL</t>
+    <t>MySQL</t>
   </si>
   <si>
     <t>#120248</t>
@@ -385,7 +385,7 @@
     <t>https://bugs.mysql.com/bug.php?id=121208</t>
   </si>
   <si>
-    <t>PERCONA</t>
+    <t>Percona</t>
   </si>
   <si>
     <t>PS-11056</t>
@@ -481,7 +481,7 @@
     <t>https://perconadev.atlassian.net/browse/PS-11555</t>
   </si>
   <si>
-    <t>polardbx-sql</t>
+    <t>PolarDB</t>
   </si>
   <si>
     <t>#268</t>
@@ -544,7 +544,7 @@
     <t>https://github.com/polardb/polardbx-sql/issues/297</t>
   </si>
   <si>
-    <t>TIDB</t>
+    <t>TiDB</t>
   </si>
   <si>
     <t>#70633</t>
@@ -598,7 +598,7 @@
     <t>https://github.com/openlink/virtuoso-opensource/issues/1438</t>
   </si>
   <si>
-    <t>Vitness</t>
+    <t>Vitess</t>
   </si>
   <si>
     <t>#20611</t>
@@ -1859,7 +1859,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G94"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="16" style="1" customWidth="1"/>
     <col min="2" max="2" width="8" style="1" customWidth="1"/>
@@ -4037,7 +4037,7 @@
     <dataValidation type="list" sqref="E2:E94">
       <formula1>"Simplification,Logical Bug"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="F2:F11 F12:F14 F15:F94">
+    <dataValidation type="list" sqref="F2:F94">
       <formula1>"Confirmed,Fixed,Waiting,Duplicated,Not a bug"</formula1>
     </dataValidation>
   </dataValidations>

--- a/founded bug/data/VECT.xlsx
+++ b/founded bug/data/VECT.xlsx
@@ -448,163 +448,163 @@
     <t>https://perconadev.atlassian.net/browse/PS-11550</t>
   </si>
   <si>
+    <t>PS-11551</t>
+  </si>
+  <si>
+    <t>https://perconadev.atlassian.net/browse/PS-11551</t>
+  </si>
+  <si>
+    <t>PS-11552</t>
+  </si>
+  <si>
+    <t>https://perconadev.atlassian.net/browse/PS-11552</t>
+  </si>
+  <si>
+    <t>PS-11553</t>
+  </si>
+  <si>
+    <t>https://perconadev.atlassian.net/browse/PS-11553</t>
+  </si>
+  <si>
+    <t>PS-11554</t>
+  </si>
+  <si>
+    <t>https://perconadev.atlassian.net/browse/PS-11554</t>
+  </si>
+  <si>
+    <t>PS-11555</t>
+  </si>
+  <si>
+    <t>https://perconadev.atlassian.net/browse/PS-11555</t>
+  </si>
+  <si>
+    <t>PolarDB</t>
+  </si>
+  <si>
+    <t>#268</t>
+  </si>
+  <si>
+    <t>https://github.com/polardb/polardbx-sql/issues/268</t>
+  </si>
+  <si>
+    <t>#269</t>
+  </si>
+  <si>
+    <t>https://github.com/polardb/polardbx-sql/issues/269</t>
+  </si>
+  <si>
+    <t>#286</t>
+  </si>
+  <si>
+    <t>https://github.com/polardb/polardbx-sql/issues/286</t>
+  </si>
+  <si>
+    <t>#287</t>
+  </si>
+  <si>
+    <t>https://github.com/polardb/polardbx-sql/issues/287</t>
+  </si>
+  <si>
+    <t>#288</t>
+  </si>
+  <si>
+    <t>https://github.com/polardb/polardbx-sql/issues/288</t>
+  </si>
+  <si>
+    <t>#289</t>
+  </si>
+  <si>
+    <t>https://github.com/polardb/polardbx-sql/issues/289</t>
+  </si>
+  <si>
+    <t>#290</t>
+  </si>
+  <si>
+    <t>https://github.com/polardb/polardbx-sql/issues/290</t>
+  </si>
+  <si>
+    <t>#291</t>
+  </si>
+  <si>
+    <t>https://github.com/polardb/polardbx-sql/issues/291</t>
+  </si>
+  <si>
+    <t>#292</t>
+  </si>
+  <si>
+    <t>https://github.com/polardb/polardbx-sql/issues/292</t>
+  </si>
+  <si>
+    <t>#297</t>
+  </si>
+  <si>
+    <t>https://github.com/polardb/polardbx-sql/issues/297</t>
+  </si>
+  <si>
+    <t>TiDB</t>
+  </si>
+  <si>
+    <t>#70633</t>
+  </si>
+  <si>
+    <t>https://github.com/pingcap/tidb/issues/70633</t>
+  </si>
+  <si>
+    <t>#70634</t>
+  </si>
+  <si>
+    <t>https://github.com/pingcap/tidb/issues/70634</t>
+  </si>
+  <si>
+    <t>#70636</t>
+  </si>
+  <si>
+    <t>https://github.com/pingcap/tidb/issues/70636</t>
+  </si>
+  <si>
+    <t>#70641</t>
+  </si>
+  <si>
+    <t>https://github.com/pingcap/tidb/issues/70641</t>
+  </si>
+  <si>
+    <t>#70745</t>
+  </si>
+  <si>
+    <t>https://github.com/pingcap/tidb/issues/70745</t>
+  </si>
+  <si>
+    <t>#70746</t>
+  </si>
+  <si>
+    <t>https://github.com/pingcap/tidb/issues/70746</t>
+  </si>
+  <si>
+    <t>Virtuoso</t>
+  </si>
+  <si>
+    <t>#1437</t>
+  </si>
+  <si>
+    <t>https://github.com/openlink/virtuoso-opensource/issues/1437</t>
+  </si>
+  <si>
+    <t>#1438</t>
+  </si>
+  <si>
+    <t>https://github.com/openlink/virtuoso-opensource/issues/1438</t>
+  </si>
+  <si>
+    <t>Vitess</t>
+  </si>
+  <si>
+    <t>#20611</t>
+  </si>
+  <si>
+    <t>https://github.com/vitessio/vitess/issues/20611</t>
+  </si>
+  <si>
     <t>Waiting</t>
-  </si>
-  <si>
-    <t>PS-11551</t>
-  </si>
-  <si>
-    <t>https://perconadev.atlassian.net/browse/PS-11551</t>
-  </si>
-  <si>
-    <t>PS-11552</t>
-  </si>
-  <si>
-    <t>https://perconadev.atlassian.net/browse/PS-11552</t>
-  </si>
-  <si>
-    <t>PS-11553</t>
-  </si>
-  <si>
-    <t>https://perconadev.atlassian.net/browse/PS-11553</t>
-  </si>
-  <si>
-    <t>PS-11554</t>
-  </si>
-  <si>
-    <t>https://perconadev.atlassian.net/browse/PS-11554</t>
-  </si>
-  <si>
-    <t>PS-11555</t>
-  </si>
-  <si>
-    <t>https://perconadev.atlassian.net/browse/PS-11555</t>
-  </si>
-  <si>
-    <t>PolarDB</t>
-  </si>
-  <si>
-    <t>#268</t>
-  </si>
-  <si>
-    <t>https://github.com/polardb/polardbx-sql/issues/268</t>
-  </si>
-  <si>
-    <t>#269</t>
-  </si>
-  <si>
-    <t>https://github.com/polardb/polardbx-sql/issues/269</t>
-  </si>
-  <si>
-    <t>#286</t>
-  </si>
-  <si>
-    <t>https://github.com/polardb/polardbx-sql/issues/286</t>
-  </si>
-  <si>
-    <t>#287</t>
-  </si>
-  <si>
-    <t>https://github.com/polardb/polardbx-sql/issues/287</t>
-  </si>
-  <si>
-    <t>#288</t>
-  </si>
-  <si>
-    <t>https://github.com/polardb/polardbx-sql/issues/288</t>
-  </si>
-  <si>
-    <t>#289</t>
-  </si>
-  <si>
-    <t>https://github.com/polardb/polardbx-sql/issues/289</t>
-  </si>
-  <si>
-    <t>#290</t>
-  </si>
-  <si>
-    <t>https://github.com/polardb/polardbx-sql/issues/290</t>
-  </si>
-  <si>
-    <t>#291</t>
-  </si>
-  <si>
-    <t>https://github.com/polardb/polardbx-sql/issues/291</t>
-  </si>
-  <si>
-    <t>#292</t>
-  </si>
-  <si>
-    <t>https://github.com/polardb/polardbx-sql/issues/292</t>
-  </si>
-  <si>
-    <t>#297</t>
-  </si>
-  <si>
-    <t>https://github.com/polardb/polardbx-sql/issues/297</t>
-  </si>
-  <si>
-    <t>TiDB</t>
-  </si>
-  <si>
-    <t>#70633</t>
-  </si>
-  <si>
-    <t>https://github.com/pingcap/tidb/issues/70633</t>
-  </si>
-  <si>
-    <t>#70634</t>
-  </si>
-  <si>
-    <t>https://github.com/pingcap/tidb/issues/70634</t>
-  </si>
-  <si>
-    <t>#70636</t>
-  </si>
-  <si>
-    <t>https://github.com/pingcap/tidb/issues/70636</t>
-  </si>
-  <si>
-    <t>#70641</t>
-  </si>
-  <si>
-    <t>https://github.com/pingcap/tidb/issues/70641</t>
-  </si>
-  <si>
-    <t>#70745</t>
-  </si>
-  <si>
-    <t>https://github.com/pingcap/tidb/issues/70745</t>
-  </si>
-  <si>
-    <t>#70746</t>
-  </si>
-  <si>
-    <t>https://github.com/pingcap/tidb/issues/70746</t>
-  </si>
-  <si>
-    <t>Virtuoso</t>
-  </si>
-  <si>
-    <t>#1437</t>
-  </si>
-  <si>
-    <t>https://github.com/openlink/virtuoso-opensource/issues/1437</t>
-  </si>
-  <si>
-    <t>#1438</t>
-  </si>
-  <si>
-    <t>https://github.com/openlink/virtuoso-opensource/issues/1438</t>
-  </si>
-  <si>
-    <t>Vitess</t>
-  </si>
-  <si>
-    <t>#20611</t>
-  </si>
-  <si>
-    <t>https://github.com/vitessio/vitess/issues/20611</t>
   </si>
   <si>
     <t>#20612</t>
@@ -3267,7 +3267,7 @@
         <v>10</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>138</v>
+        <v>11</v>
       </c>
       <c r="G61" s="7" t="s">
         <v>12</v>
@@ -3281,16 +3281,16 @@
         <v>11</v>
       </c>
       <c r="C62" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="D62" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="D62" s="6" t="s">
-        <v>140</v>
-      </c>
       <c r="E62" s="5" t="s">
         <v>10</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>138</v>
+        <v>11</v>
       </c>
       <c r="G62" s="7" t="s">
         <v>12</v>
@@ -3304,16 +3304,16 @@
         <v>12</v>
       </c>
       <c r="C63" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="D63" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="D63" s="6" t="s">
-        <v>142</v>
-      </c>
       <c r="E63" s="5" t="s">
         <v>10</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>138</v>
+        <v>11</v>
       </c>
       <c r="G63" s="7" t="s">
         <v>12</v>
@@ -3327,16 +3327,16 @@
         <v>13</v>
       </c>
       <c r="C64" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="D64" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="D64" s="6" t="s">
-        <v>144</v>
-      </c>
       <c r="E64" s="5" t="s">
         <v>10</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>138</v>
+        <v>11</v>
       </c>
       <c r="G64" s="7" t="s">
         <v>12</v>
@@ -3350,16 +3350,16 @@
         <v>14</v>
       </c>
       <c r="C65" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D65" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="D65" s="6" t="s">
-        <v>146</v>
-      </c>
       <c r="E65" s="5" t="s">
         <v>10</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>138</v>
+        <v>11</v>
       </c>
       <c r="G65" s="7" t="s">
         <v>12</v>
@@ -3373,16 +3373,16 @@
         <v>15</v>
       </c>
       <c r="C66" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="D66" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="D66" s="6" t="s">
-        <v>148</v>
-      </c>
       <c r="E66" s="5" t="s">
         <v>10</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>138</v>
+        <v>11</v>
       </c>
       <c r="G66" s="7" t="s">
         <v>12</v>
@@ -3390,16 +3390,16 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B67" s="4">
         <v>1</v>
       </c>
       <c r="C67" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D67" s="6" t="s">
         <v>150</v>
-      </c>
-      <c r="D67" s="6" t="s">
-        <v>151</v>
       </c>
       <c r="E67" s="5" t="s">
         <v>10</v>
@@ -3413,16 +3413,16 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B68" s="4">
         <v>2</v>
       </c>
       <c r="C68" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="D68" s="6" t="s">
         <v>152</v>
-      </c>
-      <c r="D68" s="6" t="s">
-        <v>153</v>
       </c>
       <c r="E68" s="5" t="s">
         <v>10</v>
@@ -3436,16 +3436,16 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B69" s="4">
         <v>3</v>
       </c>
       <c r="C69" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="D69" s="6" t="s">
         <v>154</v>
-      </c>
-      <c r="D69" s="6" t="s">
-        <v>155</v>
       </c>
       <c r="E69" s="5" t="s">
         <v>10</v>
@@ -3459,16 +3459,16 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B70" s="4">
         <v>4</v>
       </c>
       <c r="C70" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D70" s="6" t="s">
         <v>156</v>
-      </c>
-      <c r="D70" s="6" t="s">
-        <v>157</v>
       </c>
       <c r="E70" s="5" t="s">
         <v>10</v>
@@ -3482,16 +3482,16 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B71" s="4">
         <v>5</v>
       </c>
       <c r="C71" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="D71" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="D71" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="E71" s="5" t="s">
         <v>10</v>
@@ -3505,16 +3505,16 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B72" s="4">
         <v>6</v>
       </c>
       <c r="C72" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="D72" s="6" t="s">
         <v>160</v>
-      </c>
-      <c r="D72" s="6" t="s">
-        <v>161</v>
       </c>
       <c r="E72" s="5" t="s">
         <v>10</v>
@@ -3528,16 +3528,16 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B73" s="4">
         <v>7</v>
       </c>
       <c r="C73" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="D73" s="6" t="s">
         <v>162</v>
-      </c>
-      <c r="D73" s="6" t="s">
-        <v>163</v>
       </c>
       <c r="E73" s="5" t="s">
         <v>10</v>
@@ -3551,16 +3551,16 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B74" s="4">
         <v>8</v>
       </c>
       <c r="C74" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="D74" s="6" t="s">
         <v>164</v>
-      </c>
-      <c r="D74" s="6" t="s">
-        <v>165</v>
       </c>
       <c r="E74" s="5" t="s">
         <v>10</v>
@@ -3574,16 +3574,16 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B75" s="4">
         <v>9</v>
       </c>
       <c r="C75" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="D75" s="6" t="s">
         <v>166</v>
-      </c>
-      <c r="D75" s="6" t="s">
-        <v>167</v>
       </c>
       <c r="E75" s="5" t="s">
         <v>10</v>
@@ -3597,16 +3597,16 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B76" s="4">
         <v>10</v>
       </c>
       <c r="C76" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D76" s="6" t="s">
         <v>168</v>
-      </c>
-      <c r="D76" s="6" t="s">
-        <v>169</v>
       </c>
       <c r="E76" s="5" t="s">
         <v>10</v>
@@ -3620,16 +3620,16 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B77" s="4">
         <v>1</v>
       </c>
       <c r="C77" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="D77" s="6" t="s">
         <v>171</v>
-      </c>
-      <c r="D77" s="6" t="s">
-        <v>172</v>
       </c>
       <c r="E77" s="5" t="s">
         <v>10</v>
@@ -3643,16 +3643,16 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B78" s="4">
         <v>2</v>
       </c>
       <c r="C78" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D78" s="6" t="s">
         <v>173</v>
-      </c>
-      <c r="D78" s="6" t="s">
-        <v>174</v>
       </c>
       <c r="E78" s="5" t="s">
         <v>10</v>
@@ -3666,16 +3666,16 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B79" s="4">
         <v>3</v>
       </c>
       <c r="C79" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="D79" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="D79" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="E79" s="5" t="s">
         <v>10</v>
@@ -3689,16 +3689,16 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B80" s="4">
         <v>4</v>
       </c>
       <c r="C80" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="D80" s="6" t="s">
         <v>177</v>
-      </c>
-      <c r="D80" s="6" t="s">
-        <v>178</v>
       </c>
       <c r="E80" s="5" t="s">
         <v>10</v>
@@ -3712,16 +3712,16 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B81" s="4">
         <v>5</v>
       </c>
       <c r="C81" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="D81" s="6" t="s">
         <v>179</v>
-      </c>
-      <c r="D81" s="6" t="s">
-        <v>180</v>
       </c>
       <c r="E81" s="5" t="s">
         <v>10</v>
@@ -3735,16 +3735,16 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B82" s="4">
         <v>6</v>
       </c>
       <c r="C82" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="D82" s="6" t="s">
         <v>181</v>
-      </c>
-      <c r="D82" s="6" t="s">
-        <v>182</v>
       </c>
       <c r="E82" s="5" t="s">
         <v>10</v>
@@ -3758,16 +3758,16 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B83" s="4">
         <v>1</v>
       </c>
       <c r="C83" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D83" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="D83" s="6" t="s">
-        <v>185</v>
       </c>
       <c r="E83" s="5" t="s">
         <v>10</v>
@@ -3781,16 +3781,16 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B84" s="4">
         <v>2</v>
       </c>
       <c r="C84" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="D84" s="6" t="s">
         <v>186</v>
-      </c>
-      <c r="D84" s="6" t="s">
-        <v>187</v>
       </c>
       <c r="E84" s="5" t="s">
         <v>10</v>
@@ -3804,22 +3804,22 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B85" s="4">
         <v>1</v>
       </c>
       <c r="C85" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="D85" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="D85" s="6" t="s">
+      <c r="E85" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F85" s="5" t="s">
         <v>190</v>
-      </c>
-      <c r="E85" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F85" s="5" t="s">
-        <v>138</v>
       </c>
       <c r="G85" s="7" t="s">
         <v>12</v>
@@ -3827,7 +3827,7 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B86" s="4">
         <v>2</v>
@@ -3842,7 +3842,7 @@
         <v>10</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>138</v>
+        <v>190</v>
       </c>
       <c r="G86" s="7" t="s">
         <v>12</v>
@@ -3850,7 +3850,7 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B87" s="4">
         <v>3</v>
@@ -3865,7 +3865,7 @@
         <v>10</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>138</v>
+        <v>190</v>
       </c>
       <c r="G87" s="7" t="s">
         <v>12</v>
@@ -3873,7 +3873,7 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B88" s="4">
         <v>4</v>
@@ -3888,7 +3888,7 @@
         <v>10</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>138</v>
+        <v>190</v>
       </c>
       <c r="G88" s="7" t="s">
         <v>12</v>
@@ -3896,7 +3896,7 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B89" s="4">
         <v>5</v>
@@ -3911,7 +3911,7 @@
         <v>10</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>138</v>
+        <v>190</v>
       </c>
       <c r="G89" s="7" t="s">
         <v>12</v>
@@ -3919,7 +3919,7 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B90" s="4">
         <v>6</v>
@@ -3934,7 +3934,7 @@
         <v>10</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>138</v>
+        <v>190</v>
       </c>
       <c r="G90" s="7" t="s">
         <v>12</v>
@@ -3942,7 +3942,7 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B91" s="4">
         <v>7</v>
@@ -3957,7 +3957,7 @@
         <v>10</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>138</v>
+        <v>190</v>
       </c>
       <c r="G91" s="7" t="s">
         <v>12</v>
@@ -3965,7 +3965,7 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B92" s="4">
         <v>8</v>
@@ -3980,7 +3980,7 @@
         <v>10</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>138</v>
+        <v>190</v>
       </c>
       <c r="G92" s="7" t="s">
         <v>12</v>
@@ -3988,7 +3988,7 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B93" s="4">
         <v>9</v>
@@ -4011,7 +4011,7 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B94" s="4">
         <v>10</v>
